--- a/upload/report/test_hiraoka13.xlsx
+++ b/upload/report/test_hiraoka13.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="29">
   <si>
     <t>Purchase order items PDF to Excel</t>
   </si>
@@ -23,7 +23,16 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02 19:27:53</t>
+    <t>2024-04-03 11:34:49</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>#Order</t>
   </si>
   <si>
     <t>Num</t>
@@ -44,7 +53,16 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Product</t>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>IMPORTACIONES HIRAOKA S.A.C.</t>
+  </si>
+  <si>
+    <t>CALLE 5, MZ. D-1, LOTE 5 - COOP., LAS VER VILLA EL SALVADOR</t>
+  </si>
+  <si>
+    <t>132924</t>
   </si>
   <si>
     <t>1</t>
@@ -59,7 +77,13 @@
     <t>36</t>
   </si>
   <si>
-    <t xml:space="preserve"> 503.5200 18,126.72MONITOR LED LG-27MS500-B 8 10 10 8</t>
+    <t>503.5200</t>
+  </si>
+  <si>
+    <t>18,126.72</t>
+  </si>
+  <si>
+    <t>MONITOR LED LG-27MS500-B</t>
   </si>
   <si>
     <t>2</t>
@@ -74,7 +98,10 @@
     <t>1,295.8900</t>
   </si>
   <si>
-    <t xml:space="preserve"> 3,887.67MONITOR LED GAMING LG-34GP63A-B 3</t>
+    <t>3,887.67</t>
+  </si>
+  <si>
+    <t>MONITOR LED GAMING LG-34GP63A-B</t>
   </si>
 </sst>
 </file>
@@ -414,15 +441,15 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -430,7 +457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -452,45 +479,78 @@
       <c r="G4" t="s">
         <v>9</v>
       </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
         <v>18</v>
       </c>
-      <c r="F6"/>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
